--- a/output/pdf_financials_xlsx/SLO.xlsx
+++ b/output/pdf_financials_xlsx/SLO.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.059167</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.059167</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.059167</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.059167</v>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.059167</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.046375</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.09006</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.366888</v>
       </c>
     </row>
     <row r="93">
@@ -2994,7 +2994,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3339,7 +3343,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.046375</v>
       </c>
@@ -4679,10 +4687,10 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.199331</v>
+        <v>-0.199331</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.059167</v>
+        <v>-0.059167</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SLO.xlsx
+++ b/output/pdf_financials_xlsx/SLO.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.057019</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010042</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.682624</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.057019</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010042</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.682624</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.057019</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010042</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.682624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">

--- a/output/pdf_financials_xlsx/SLO.xlsx
+++ b/output/pdf_financials_xlsx/SLO.xlsx
@@ -2075,7 +2075,7 @@
         <v>0.013547</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
     </row>
     <row r="102">
@@ -2155,7 +2155,7 @@
         <v>0.01219</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.019162</v>
+        <v>0.019819</v>
       </c>
     </row>
     <row r="107">
@@ -3568,7 +3568,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
